--- a/data/output/stats-fray-summer_2026.xlsx
+++ b/data/output/stats-fray-summer_2026.xlsx
@@ -4659,12 +4659,12 @@
           <t>Team OPS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Through Date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Workbook Season</t>
         </is>

--- a/data/output/stats-fray-summer_2026.xlsx
+++ b/data/output/stats-fray-summer_2026.xlsx
@@ -12,28 +12,28 @@
     <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cyclo Summer 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cyclo Summer 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cyclo Summer 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cyclo Summer 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cyclo Summer 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cyclo Summer 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cyclo Summer 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cyclo Summer 2026 Game 7" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Cyclo Summer 2026 Game 8" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cyclo Summer 2026 Game 8" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cyclo Summer 2026 Game 7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cyclo Summer 2026 Game 6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cyclo Summer 2026 Game 5" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cyclo Summer 2026 Game 4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cyclo Summer 2026 Game 3" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cyclo Summer 2026 Game 2" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cyclo Summer 2026 Game 1" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Summer 2026 Total'!$A$1:$Q$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Summer 2026 Game 1'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Summer 2026 Game 2'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Summer 2026 Game 3'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Summer 2026 Game 4'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Summer 2026 Game 5'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Summer 2026 Game 6'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Summer 2026 Game 7'!$A$1:$Q$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Summer 2026 Game 8'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Summer 2026 Game 8'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Summer 2026 Game 7'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Summer 2026 Game 6'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Summer 2026 Game 5'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Summer 2026 Game 4'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Summer 2026 Game 3'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Summer 2026 Game 2'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Summer 2026 Game 1'!$A$1:$Q$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -899,13 +899,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -926,55 +926,55 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -986,10 +986,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1015,14 +1015,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1078,14 +1078,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1115,46 +1115,46 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Chance</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1182,29 +1182,29 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.400</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.800</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1277,10 +1277,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1301,49 +1301,49 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kat</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1367,46 +1367,46 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1427,36 +1427,36 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1466,10 +1466,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1586,28 +1586,28 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0</v>
@@ -1616,29 +1616,29 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.516</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.516</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>0.806</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>0.923</t>
+          <t>1.322</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1774,13 +1774,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1804,33 +1804,33 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1840,19 +1840,19 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1864,24 +1864,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1893,29 +1893,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1927,29 +1927,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.333</t>
         </is>
       </c>
     </row>
@@ -1960,19 +1960,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1990,29 +1990,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -2023,19 +2023,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2053,10 +2053,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2070,32 +2070,32 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2116,36 +2116,36 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2155,10 +2155,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2182,26 +2182,26 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2242,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2271,20 +2271,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2305,55 +2305,55 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2368,58 +2368,58 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2431,160 +2431,97 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3.333</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="B14" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0.683</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0.683</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0.927</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1.610</t>
+      <c r="D14" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.607</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1.107</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.714</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2596,7 +2533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2718,16 +2655,16 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2742,40 +2679,40 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -2784,10 +2721,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2799,13 +2736,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2817,49 +2754,49 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2868,19 +2805,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2890,30 +2827,30 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2922,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2934,33 +2871,33 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.167</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2970,13 +2907,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2997,49 +2934,49 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -3051,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -3064,42 +3001,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3111,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3120,52 +3057,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -3200,32 +3137,32 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3234,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3246,52 +3183,52 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3300,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3309,19 +3246,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -3331,264 +3268,75 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pete</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
           <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.476</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.476</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0.857</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1.333</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>3.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.710</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1.097</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1.807</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3600,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3722,13 +3470,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -3746,29 +3494,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
@@ -3779,10 +3527,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -3809,52 +3557,52 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3863,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3872,52 +3620,52 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3926,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3935,52 +3683,52 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.833</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3998,49 +3746,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>1.167</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -4061,36 +3809,36 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -4100,13 +3848,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4124,52 +3872,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4178,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -4204,26 +3952,26 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -4250,46 +3998,46 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.750</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -4298,13 +4046,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4313,24 +4061,24 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -4342,20 +4090,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -4367,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4376,223 +4124,97 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.500</t>
+          <t>0.333</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E16" s="2" t="n">
+      <c r="B14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0.655</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.655</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0.828</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1.483</t>
+      <c r="M14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.577</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.577</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.423</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9443,7 +9065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9565,13 +9187,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -9589,29 +9211,29 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -9622,10 +9244,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -9652,52 +9274,52 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -9706,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -9715,52 +9337,52 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -9769,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -9778,52 +9400,52 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -9841,49 +9463,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -9904,36 +9526,36 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -9943,13 +9565,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -9967,52 +9589,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -10021,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -10047,26 +9669,26 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -10093,46 +9715,46 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>1.750</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -10141,13 +9763,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10156,24 +9778,24 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -10185,131 +9807,257 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Pete</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="B16" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.577</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.577</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.846</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1.423</t>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.655</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0.828</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.483</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10321,7 +10069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10443,16 +10191,16 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -10467,40 +10215,40 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.667</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -10509,10 +10257,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -10524,13 +10272,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -10542,49 +10290,49 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1.333</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -10593,19 +10341,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -10615,30 +10363,30 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -10647,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -10659,33 +10407,33 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.167</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -10695,13 +10443,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -10722,49 +10470,49 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -10776,7 +10524,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -10789,42 +10537,42 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -10836,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -10845,52 +10593,52 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.417</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -10925,32 +10673,32 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -10959,7 +10707,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10971,160 +10719,349 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pete</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.476</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.476</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0.857</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1.333</t>
+      <c r="B16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0.710</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.710</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1.097</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1.807</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11136,7 +11073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11255,13 +11192,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -11273,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -11285,33 +11222,33 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -11321,19 +11258,19 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -11345,24 +11282,24 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -11374,29 +11311,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -11408,29 +11345,29 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2.333</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3.333</t>
         </is>
       </c>
     </row>
@@ -11441,19 +11378,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -11471,29 +11408,29 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -11504,19 +11441,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -11534,10 +11471,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -11551,32 +11488,32 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -11588,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -11597,36 +11534,36 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -11636,10 +11573,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -11663,26 +11600,26 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -11693,16 +11630,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -11723,10 +11660,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -11752,20 +11689,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -11777,7 +11714,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -11786,55 +11723,55 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -11849,160 +11786,223 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>1.750</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2.333</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3.333</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>0.000</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="n">
+      <c r="B15" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1.107</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1.714</t>
+      <c r="E15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.683</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.683</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0.927</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1.610</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12136,13 +12136,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -12163,55 +12163,55 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -12223,10 +12223,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -12252,14 +12252,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -12289,7 +12289,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -12315,14 +12315,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -12340,7 +12340,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -12352,46 +12352,46 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chance</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -12419,29 +12419,29 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.400</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -12475,7 +12475,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -12504,7 +12504,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -12514,10 +12514,10 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -12538,49 +12538,49 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kat</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -12604,46 +12604,46 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -12652,10 +12652,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12664,36 +12664,36 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -12703,10 +12703,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12734,22 +12734,22 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>0.667</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.667</t>
         </is>
       </c>
     </row>
@@ -12790,10 +12790,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -12823,28 +12823,28 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0</v>
@@ -12853,29 +12853,29 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>0.577</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>0.923</t>
         </is>
       </c>
     </row>
